--- a/data/trans_orig/IQ23_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ23_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47697</t>
+          <t>47752</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64003</t>
+          <t>64163</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51317</t>
+          <t>51936</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68318</t>
+          <t>68118</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103306</t>
+          <t>102722</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>127097</t>
+          <t>127054</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,3%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41720</t>
+          <t>41560</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58026</t>
+          <t>57971</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51621</t>
+          <t>51821</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68622</t>
+          <t>68003</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98565</t>
+          <t>98608</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122356</t>
+          <t>122940</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,48%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>178644</t>
+          <t>178694</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>200962</t>
+          <t>201019</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>187437</t>
+          <t>188307</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>208676</t>
+          <t>208685</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>373857</t>
+          <t>374315</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>403847</t>
+          <t>404145</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,03%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50869</t>
+          <t>50812</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73187</t>
+          <t>73137</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44478</t>
+          <t>44469</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65717</t>
+          <t>64847</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101138</t>
+          <t>100840</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>131128</t>
+          <t>130670</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90598</t>
+          <t>90545</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105564</t>
+          <t>105990</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>95690</t>
+          <t>95446</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>112037</t>
+          <t>112537</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>191763</t>
+          <t>191094</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>213563</t>
+          <t>213794</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,06%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19965</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34931</t>
+          <t>34984</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29478</t>
+          <t>28978</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45825</t>
+          <t>46069</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53481</t>
+          <t>53250</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75281</t>
+          <t>75950</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>142979</t>
+          <t>142999</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160968</t>
+          <t>160747</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>159410</t>
+          <t>160350</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>176914</t>
+          <t>176837</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>308013</t>
+          <t>308544</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>333207</t>
+          <t>334433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,26%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31089</t>
+          <t>31310</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49078</t>
+          <t>49058</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27957</t>
+          <t>28034</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45461</t>
+          <t>44521</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63721</t>
+          <t>62495</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88915</t>
+          <t>88384</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>477467</t>
+          <t>478826</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>514381</t>
+          <t>515681</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>511759</t>
+          <t>513998</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>550048</t>
+          <t>550329</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1003068</t>
+          <t>1002908</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1055854</t>
+          <t>1055340</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,67%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>160760</t>
+          <t>159460</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>197674</t>
+          <t>196315</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>169431</t>
+          <t>169150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207720</t>
+          <t>205481</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>338766</t>
+          <t>339280</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>391552</t>
+          <t>391712</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60277</t>
+          <t>61506</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80339</t>
+          <t>80574</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62532</t>
+          <t>64134</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83482</t>
+          <t>83111</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>130202</t>
+          <t>130990</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158738</t>
+          <t>157954</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,08%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66422</t>
+          <t>66187</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86484</t>
+          <t>85255</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61840</t>
+          <t>62211</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82790</t>
+          <t>81188</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>133345</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161881</t>
+          <t>161093</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,15%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>164102</t>
+          <t>163483</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>185631</t>
+          <t>186049</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>184506</t>
+          <t>184114</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>209350</t>
+          <t>208728</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>355835</t>
+          <t>355121</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>388432</t>
+          <t>388520</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,02%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49832</t>
+          <t>49414</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>71361</t>
+          <t>71980</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59641</t>
+          <t>60263</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84485</t>
+          <t>84877</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>116023</t>
+          <t>115935</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>148620</t>
+          <t>149334</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113827</t>
+          <t>113489</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130584</t>
+          <t>130857</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>108262</t>
+          <t>108571</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126856</t>
+          <t>126155</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>228060</t>
+          <t>228726</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>252688</t>
+          <t>252142</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,06%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25784</t>
+          <t>25511</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42541</t>
+          <t>42879</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31715</t>
+          <t>32416</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50309</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62251</t>
+          <t>62797</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86879</t>
+          <t>86213</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,37%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>132946</t>
+          <t>133715</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>149284</t>
+          <t>150270</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>140616</t>
+          <t>140722</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>157046</t>
+          <t>156360</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>279889</t>
+          <t>280236</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>302745</t>
+          <t>302652</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,32%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22053</t>
+          <t>21067</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38391</t>
+          <t>37622</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22241</t>
+          <t>22927</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38671</t>
+          <t>38565</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47879</t>
+          <t>47972</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70735</t>
+          <t>70388</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>490168</t>
+          <t>491483</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>529356</t>
+          <t>531483</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>517703</t>
+          <t>516931</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>559539</t>
+          <t>557348</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1022475</t>
+          <t>1019954</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1079630</t>
+          <t>1078025</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,73%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>180573</t>
+          <t>178446</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>219761</t>
+          <t>218446</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>192632</t>
+          <t>194823</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>234468</t>
+          <t>235240</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>382470</t>
+          <t>384075</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>439625</t>
+          <t>442146</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53800</t>
+          <t>53865</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71123</t>
+          <t>72097</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47680</t>
+          <t>47183</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64810</t>
+          <t>64813</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>106449</t>
+          <t>106309</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131836</t>
+          <t>131164</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,84%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58244</t>
+          <t>57270</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75567</t>
+          <t>75502</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58821</t>
+          <t>58818</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75951</t>
+          <t>76448</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121163</t>
+          <t>121835</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146550</t>
+          <t>146690</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,98%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>129900</t>
+          <t>127681</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>151288</t>
+          <t>149733</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>145083</t>
+          <t>144240</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>171702</t>
+          <t>170184</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>279164</t>
+          <t>281584</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>313620</t>
+          <t>312889</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56922</t>
+          <t>58477</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78310</t>
+          <t>80529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>85733</t>
+          <t>87251</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112352</t>
+          <t>113195</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152025</t>
+          <t>152756</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>186481</t>
+          <t>184061</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,53%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>126018</t>
+          <t>126551</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146266</t>
+          <t>146563</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127174</t>
+          <t>128060</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>147141</t>
+          <t>148130</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>260775</t>
+          <t>259956</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>288831</t>
+          <t>287781</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,61%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42633</t>
+          <t>42336</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62881</t>
+          <t>62348</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39585</t>
+          <t>38596</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59552</t>
+          <t>58666</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86795</t>
+          <t>87845</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>114851</t>
+          <t>115670</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,79%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>132579</t>
+          <t>131755</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>149750</t>
+          <t>148868</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>133935</t>
+          <t>133486</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>150488</t>
+          <t>150264</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>271700</t>
+          <t>271427</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>295314</t>
+          <t>294184</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23027</t>
+          <t>23909</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40198</t>
+          <t>41022</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19961</t>
+          <t>20185</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36514</t>
+          <t>36963</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47912</t>
+          <t>49042</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71526</t>
+          <t>71799</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>461446</t>
+          <t>458336</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>500446</t>
+          <t>497620</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>474082</t>
+          <t>472693</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>515200</t>
+          <t>515355</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>939878</t>
+          <t>945678</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>999255</t>
+          <t>1002204</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,72%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198807</t>
+          <t>201633</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>237807</t>
+          <t>240917</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>223042</t>
+          <t>222887</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>264160</t>
+          <t>265549</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>438240</t>
+          <t>435291</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>497617</t>
+          <t>491817</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,21%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>9396</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18588</t>
+          <t>18474</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12238</t>
+          <t>12435</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22856</t>
+          <t>23098</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23664</t>
+          <t>23965</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38120</t>
+          <t>38135</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38478</t>
+          <t>38592</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47896</t>
+          <t>47670</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38588</t>
+          <t>38346</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49206</t>
+          <t>49009</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80390</t>
+          <t>80375</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94846</t>
+          <t>94545</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,78%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91164</t>
+          <t>91508</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111810</t>
+          <t>110962</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106379</t>
+          <t>106212</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>128417</t>
+          <t>128843</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>203998</t>
+          <t>204117</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>234453</t>
+          <t>233587</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,33%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47489</t>
+          <t>48337</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68135</t>
+          <t>67791</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54137</t>
+          <t>53711</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76175</t>
+          <t>76342</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>107400</t>
+          <t>108266</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>137855</t>
+          <t>137736</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,29%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>119627</t>
+          <t>119715</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>140710</t>
+          <t>141193</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>134525</t>
+          <t>133740</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>159333</t>
+          <t>159977</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>261015</t>
+          <t>262541</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>294800</t>
+          <t>295641</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>77,0%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32362</t>
+          <t>31879</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53445</t>
+          <t>53357</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51556</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76364</t>
+          <t>77149</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89162</t>
+          <t>88321</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>122947</t>
+          <t>121421</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,62%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>209181</t>
+          <t>209121</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>237180</t>
+          <t>237476</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>231963</t>
+          <t>231030</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>260951</t>
+          <t>262154</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>449713</t>
+          <t>447259</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>491027</t>
+          <t>490104</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,19%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33041</t>
+          <t>32745</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61040</t>
+          <t>61100</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44136</t>
+          <t>42933</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73124</t>
+          <t>74057</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>84281</t>
+          <t>85204</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>125595</t>
+          <t>128049</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>447035</t>
+          <t>447861</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>496594</t>
+          <t>495758</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>503401</t>
+          <t>504217</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>552053</t>
+          <t>554632</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>963471</t>
+          <t>967512</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1034488</t>
+          <t>1032773</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,75%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>163065</t>
+          <t>163901</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>212624</t>
+          <t>211798</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>207922</t>
+          <t>205343</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>256574</t>
+          <t>255758</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>385146</t>
+          <t>386861</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>456163</t>
+          <t>452122</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ23_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ23_R-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>60014</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>51677</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>69065</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>50,04%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>43,09%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>57,58%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>55466</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>47752</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>64163</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>47222</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>64062</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>52,46%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>45,17%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>60,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>60014</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>51936</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>68118</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>50,04%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102722</t>
+          <t>104223</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>127054</t>
+          <t>127955</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,7%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>59925</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>50874</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>68262</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>49,96%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>42,42%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>56,91%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>50257</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>41560</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>57971</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>41661</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>58501</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>47,54%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>39,31%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>54,83%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>59925</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>51821</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>68003</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>49,96%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98608</t>
+          <t>97707</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122940</t>
+          <t>121439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>53,81%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>119939</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>119939</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>119939</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>105723</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>105723</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>105723</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>119939</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>119939</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>119939</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>198824</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>188192</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>208822</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>78,54%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>74,34%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>82,49%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>283</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>190624</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>178694</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>201019</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>178931</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>201197</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>75,7%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>70,96%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>79,82%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>198824</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>188307</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>208685</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>78,54%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>374315</t>
+          <t>373065</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>404145</t>
+          <t>403738</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,95%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>54330</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>44332</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>64962</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>21,46%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17,51%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>25,66%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>61207</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>50812</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>73137</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>50634</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>72900</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>24,3%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>20,18%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>29,04%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>54330</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>44469</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>64847</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>21,46%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>100840</t>
+          <t>101247</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>130670</t>
+          <t>131920</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253154</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253154</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253154</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>377</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>251831</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>251831</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>251831</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253154</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253154</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253154</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>104367</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>95406</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>112099</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>73,75%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>67,42%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>79,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>98755</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>90545</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>105990</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>91279</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>105814</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>78,67%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>72,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>84,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>104367</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>95446</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>112537</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>73,75%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>191094</t>
+          <t>192173</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>213794</t>
+          <t>213007</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,76%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>37148</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>29416</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>46109</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>26,25%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>20,79%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>32,58%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>26774</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>19539</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>34984</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>19715</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>34250</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>21,33%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,57%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>27,87%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>37148</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>28978</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>46069</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>26,25%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53250</t>
+          <t>54037</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75950</t>
+          <t>74871</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>125529</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>125529</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>125529</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>169162</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>158885</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>176826</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>82,57%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>77,55%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>86,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>152327</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>142999</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>160747</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>142776</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>161432</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>79,31%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>74,46%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>83,7%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>169162</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>160350</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>176837</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>82,57%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>308544</t>
+          <t>307156</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>334433</t>
+          <t>333579</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,04%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>35709</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>28045</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>45986</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>17,43%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>13,69%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>22,45%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>39730</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>31310</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>49058</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>30625</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>49281</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>20,69%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16,3%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>25,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>35709</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>28034</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>44521</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>17,43%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62495</t>
+          <t>63349</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88384</t>
+          <t>89772</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>204871</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>204871</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>204871</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>283</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>192057</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>192057</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>192057</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>204871</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>204871</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>204871</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,74 +2095,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>532368</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>513235</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>551237</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>73,99%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>71,33%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>76,62%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>497172</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>478826</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>515681</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>480522</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>515664</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>73,64%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>70,92%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>71,17%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>76,38%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>798</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>532368</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>513998</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>550329</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>73,99%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>71,44%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>76,49%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1535</t>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1002908</t>
+          <t>1003723</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1055340</t>
+          <t>1057093</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>187111</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>168242</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>206244</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,01%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23,38%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>28,67%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>177969</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>159460</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>196315</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>159477</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>194619</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>26,36%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>23,62%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>29,08%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>187111</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>169150</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>205481</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>26,01%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>23,51%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>339280</t>
+          <t>337527</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>391712</t>
+          <t>390897</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>719479</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>719479</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>719479</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1009</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>675141</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>675141</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>675141</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>719479</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>719479</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>719479</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>72864</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>62261</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>83204</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>50,14%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>42,84%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>57,26%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>70904</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>61506</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>80574</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>59805</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>81309</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>48,31%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>41,91%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>54,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>72864</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>64134</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>83111</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>50,14%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>130990</t>
+          <t>130425</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>157954</t>
+          <t>158170</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>72458</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>62118</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>83061</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>49,86%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>42,74%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>57,16%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>75857</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>66187</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>85255</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>65452</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>86956</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>51,69%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>45,1%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>58,09%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>72458</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>62211</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>81188</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>49,86%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>134129</t>
+          <t>133913</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161093</t>
+          <t>161658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,35%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>145322</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>145322</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>145322</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>145322</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>145322</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>145322</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>197155</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>184732</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>209118</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>73,29%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>68,68%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>77,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>174836</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>163483</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>186049</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>163567</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>185446</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>74,25%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>69,43%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>79,01%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>197155</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>184114</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>208728</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>73,29%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>355121</t>
+          <t>355582</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>388520</t>
+          <t>388552</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>71836</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>59873</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>84259</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>26,71%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>22,26%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>31,32%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>60627</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>49414</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>71980</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>50017</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>71896</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>25,75%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>20,99%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>71836</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>60263</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>84877</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>26,71%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>115935</t>
+          <t>115903</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149334</t>
+          <t>148873</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>339</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>235463</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>235463</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>235463</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>118208</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>107859</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>126379</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>74,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>68,02%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>79,7%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>123108</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>113489</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>130857</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>114328</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>130843</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>78,73%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>72,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>83,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>118208</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>108571</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>126155</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>74,55%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>228726</t>
+          <t>228602</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>252142</t>
+          <t>253716</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,56%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>40363</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>32192</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>50712</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>25,45%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>20,3%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>31,98%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>33260</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>25511</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>42879</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>25525</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>42040</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>21,27%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>16,31%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>27,42%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>40363</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>32416</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>50000</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>25,45%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62797</t>
+          <t>61223</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86213</t>
+          <t>86337</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>156368</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>156368</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>156368</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>149728</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>141402</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>157299</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>83,51%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>78,87%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>87,74%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>142103</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>133715</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>150270</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>132985</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>150080</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>82,94%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>78,04%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>87,7%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>149728</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>140722</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>156360</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>83,51%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>280236</t>
+          <t>279666</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>302652</t>
+          <t>303689</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,61%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29559</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21988</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>37885</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16,49%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12,26%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>21,13%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>29234</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>21067</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>37622</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>21257</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>38352</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>17,06%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12,3%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>21,96%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>29559</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>22927</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>38565</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>16,49%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47972</t>
+          <t>46935</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70388</t>
+          <t>70958</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179287</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179287</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179287</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179287</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179287</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179287</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>537955</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>516946</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>557406</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>71,52%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>68,73%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>74,11%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>731</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>510951</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>491483</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>531483</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>490900</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>528676</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>71,97%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>69,23%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>74,86%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>766</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>537955</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>516931</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>557348</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>71,52%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1019954</t>
+          <t>1019157</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1078025</t>
+          <t>1074094</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,46%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>214216</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>194765</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>235225</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>28,48%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,89%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>31,27%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>292</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>198978</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>178446</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>218446</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>181253</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>219029</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>28,03%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>25,14%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>30,77%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>214216</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>194823</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>235240</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>28,48%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>384075</t>
+          <t>388006</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>442146</t>
+          <t>442943</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>752171</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>752171</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>752171</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1023</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>709929</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>709929</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>709929</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1072</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>752171</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>752171</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>752171</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>56425</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>47360</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>65151</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>45,64%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>38,31%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>52,7%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>62608</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>53865</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>72097</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>53279</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>71958</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>48,4%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>41,64%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55,73%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>56425</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>47183</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>64813</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>45,64%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>106309</t>
+          <t>104862</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131164</t>
+          <t>130679</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,65%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>67206</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>58480</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>76271</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>54,36%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>47,3%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>61,69%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>66759</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>57270</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>57409</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>76088</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>51,6%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>44,27%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>58,36%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>67206</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>58818</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>76448</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>54,36%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121835</t>
+          <t>122320</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146690</t>
+          <t>148137</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>58,55%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>123631</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>123631</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>123631</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>129367</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>129367</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>129367</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>123631</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>123631</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>123631</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>157198</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>142831</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>168474</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>61,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>55,48%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>65,44%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>140167</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>127681</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>149733</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>129614</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>150455</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>67,32%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>61,32%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>71,91%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>157198</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>144240</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>170184</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>61,06%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>281584</t>
+          <t>281917</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>312889</t>
+          <t>314180</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,47%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>100237</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>88961</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>114604</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>38,94%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>34,56%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>44,52%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>68043</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>58477</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>80529</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>57755</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>78596</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>32,68%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>100237</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>87251</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>113195</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>38,94%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152756</t>
+          <t>151465</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>184061</t>
+          <t>183728</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,46%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>257435</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>257435</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>257435</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>328</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>208210</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>208210</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>208210</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>257435</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>257435</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>257435</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>137972</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>127485</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>147395</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>73,89%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>68,27%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>78,94%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>197</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>136738</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>126551</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>146563</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>126158</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>146687</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>72,39%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>66,99%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>77,59%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>137972</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>128060</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>148130</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>73,89%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>259956</t>
+          <t>259034</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>287781</t>
+          <t>286793</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,35%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>48754</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>39331</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>59241</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>26,11%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>21,06%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>31,73%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>52161</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>42336</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>62348</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>42212</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>62741</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>27,61%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>22,41%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>33,01%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>48754</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>38596</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>58666</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>26,11%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87845</t>
+          <t>88833</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115670</t>
+          <t>116592</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>186726</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>186726</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>186726</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>186726</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>186726</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>186726</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>142681</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>133932</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>150123</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>83,71%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>78,58%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>88,07%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>141082</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>131755</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>148868</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>131943</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>148975</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>81,66%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>76,26%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>86,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>142681</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>133486</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>150264</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>83,71%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>271427</t>
+          <t>270305</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>294184</t>
+          <t>294562</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,82%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27768</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20326</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>36517</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>11,93%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>21,42%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>31695</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>23909</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>41022</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>23802</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>40834</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>18,34%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>13,84%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>23,74%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>27768</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>20185</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>36963</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>16,29%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49042</t>
+          <t>48664</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71799</t>
+          <t>72921</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170449</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170449</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170449</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172777</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172777</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172777</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170449</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170449</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170449</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>494276</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>473777</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>515717</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>66,95%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>64,18%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>69,86%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>716</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>480594</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>458336</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>497620</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>461458</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>500683</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>68,73%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>65,55%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>71,16%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>494276</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>472693</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>515355</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>66,95%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>945678</t>
+          <t>945109</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1002204</t>
+          <t>1001563</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,67%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>243966</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>222525</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>264465</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>33,05%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>30,14%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>35,82%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>336</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>218659</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>201633</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>240917</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>198570</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>237795</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>31,27%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28,84%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>34,45%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>243966</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>222887</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>265549</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>33,05%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>435291</t>
+          <t>435932</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>491817</t>
+          <t>492386</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,25%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>738242</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>738242</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>738242</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1052</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>699253</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>699253</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>699253</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1055</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>738242</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>738242</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>738242</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15171</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10891</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19816</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>30,02%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>21,55%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13334</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9396</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18474</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23,37%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16,46%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>32,37%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17239</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12435</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23098</t>
+          <t>16634</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>30574</t>
+          <t>26864</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23965</t>
+          <t>21044</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38135</t>
+          <t>33043</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>35366</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>30721</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>39646</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>69,98%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>60,79%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>78,45%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>43732</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>38592</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>47670</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>76,63%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>67,63%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>83,54%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44205</t>
+          <t>40038</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38346</t>
+          <t>35097</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49009</t>
+          <t>43524</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>87936</t>
+          <t>75404</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80375</t>
+          <t>69225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94545</t>
+          <t>81224</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,42%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57066</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57066</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57066</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>51731</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>51731</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>51731</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118510</t>
+          <t>102268</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118510</t>
+          <t>102268</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118510</t>
+          <t>102268</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>103993</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>93565</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>112803</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>66,02%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>59,4%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>71,61%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>102084</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>91508</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>110962</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>64,08%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>57,44%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>69,66%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>117454</t>
+          <t>94618</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106212</t>
+          <t>86142</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>128843</t>
+          <t>103014</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>219538</t>
+          <t>198611</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>204117</t>
+          <t>184813</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>233587</t>
+          <t>210747</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>69,54%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>53529</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>44719</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>63957</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>33,98%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>28,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>40,6%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>57215</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>48337</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>67791</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>35,92%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>30,34%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>42,56%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>65100</t>
+          <t>50900</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53711</t>
+          <t>42504</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76342</t>
+          <t>59376</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>122315</t>
+          <t>104428</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>108266</t>
+          <t>92292</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>137736</t>
+          <t>118226</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>39,01%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>139529</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>127997</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>151069</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>70,28%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>64,48%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>76,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>131626</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>119715</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>141193</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>76,05%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>69,17%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>81,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>147672</t>
+          <t>134722</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>133740</t>
+          <t>123469</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>159977</t>
+          <t>143301</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>279298</t>
+          <t>274251</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>262541</t>
+          <t>258199</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>295641</t>
+          <t>288234</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,23%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>58991</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>47451</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>70523</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>29,72%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>23,9%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>35,52%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>41446</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>31879</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>53357</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>23,95%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>18,42%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>30,83%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>63217</t>
+          <t>39950</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50912</t>
+          <t>31371</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77149</t>
+          <t>51203</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>104664</t>
+          <t>98941</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88321</t>
+          <t>84958</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>121421</t>
+          <t>114993</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>198520</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>198520</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>198520</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>210889</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>210889</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>210889</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>383962</t>
+          <t>373192</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>383962</t>
+          <t>373192</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>383962</t>
+          <t>373192</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>237338</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>220907</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>249512</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>81,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>75,56%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>85,35%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>222441</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>209121</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>237476</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>82,32%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>77,39%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>87,88%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>248007</t>
+          <t>201701</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>231030</t>
+          <t>189759</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>262154</t>
+          <t>211535</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>470448</t>
+          <t>439039</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>447259</t>
+          <t>420685</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>490104</t>
+          <t>457466</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>84,12%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>55008</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>42834</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>71439</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>18,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>14,65%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>24,44%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>47780</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>32745</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>61100</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17,68%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12,12%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>22,61%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>57080</t>
+          <t>49771</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42933</t>
+          <t>39937</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74057</t>
+          <t>61713</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>104860</t>
+          <t>104779</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85204</t>
+          <t>86352</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>128049</t>
+          <t>123133</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>292346</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>292346</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>292346</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>335</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>270221</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>270221</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>270221</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305087</t>
+          <t>251472</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305087</t>
+          <t>251472</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305087</t>
+          <t>251472</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>575308</t>
+          <t>543818</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>575308</t>
+          <t>543818</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>575308</t>
+          <t>543818</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>496031</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>473783</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>518880</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>70,97%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>67,79%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>74,24%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>630</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>469486</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>447861</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>495758</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>71,17%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>67,89%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>75,15%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>530373</t>
+          <t>442733</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>504217</t>
+          <t>424474</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>554632</t>
+          <t>460390</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>999859</t>
+          <t>938765</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>967512</t>
+          <t>904712</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1032773</t>
+          <t>966284</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>73,08%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>202894</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>180045</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>225142</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>29,03%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,76%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>32,21%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>304</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>190173</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>163901</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>211798</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>28,83%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>24,85%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>32,11%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>229602</t>
+          <t>180659</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>205343</t>
+          <t>163002</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>255758</t>
+          <t>198918</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>419775</t>
+          <t>383552</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>386861</t>
+          <t>356033</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>452122</t>
+          <t>417605</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>698925</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>698925</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>698925</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>934</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>659659</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>659659</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>659659</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>759975</t>
+          <t>623392</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>759975</t>
+          <t>623392</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>759975</t>
+          <t>623392</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1419634</t>
+          <t>1322317</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1419634</t>
+          <t>1322317</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1419634</t>
+          <t>1322317</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
